--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_014.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_014.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="177">
   <si>
     <t>Sezione</t>
   </si>
@@ -278,99 +278,108 @@
     <t>residenzaOriginaria</t>
   </si>
   <si>
+    <t>Genitore</t>
+  </si>
+  <si>
+    <t>evento.madre</t>
+  </si>
+  <si>
+    <t>evento.flagOmogenitoriale,=,false</t>
+  </si>
+  <si>
+    <t>Stato di nascita</t>
+  </si>
+  <si>
+    <t>Stato di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>Provincia di nascita</t>
+  </si>
+  <si>
+    <t>Provincia di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>Comune di nascita</t>
+  </si>
+  <si>
+    <t>Comune di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>Nazionalità - Descrizione</t>
+  </si>
+  <si>
+    <t>Comprensione</t>
+  </si>
+  <si>
+    <t>tipoImpedimento</t>
+  </si>
+  <si>
+    <t>Stato di residenza</t>
+  </si>
+  <si>
+    <t>Stato di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>Provincia di residenza</t>
+  </si>
+  <si>
+    <t>Provincia di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>Comune di residenza</t>
+  </si>
+  <si>
+    <t>Comune di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>Indirizzo di residenza</t>
+  </si>
+  <si>
+    <t>flag dichiarante</t>
+  </si>
+  <si>
+    <t>flagDichiarante</t>
+  </si>
+  <si>
+    <t>flag comparente</t>
+  </si>
+  <si>
+    <t>flagComparente</t>
+  </si>
+  <si>
+    <t>flag firmatario</t>
+  </si>
+  <si>
+    <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Trasmissione residenza estera</t>
+  </si>
+  <si>
+    <t>flagTrasmissioneResidenzaEstera</t>
+  </si>
+  <si>
     <t>Madre</t>
   </si>
   <si>
-    <t>evento.madre</t>
+    <t>evento.flagOmogenitoriale,=,true</t>
+  </si>
+  <si>
+    <t>evento.padre</t>
+  </si>
+  <si>
+    <t>Padre</t>
+  </si>
+  <si>
+    <t>Madre biologica</t>
+  </si>
+  <si>
+    <t>evento.madreBiologica</t>
   </si>
   <si>
     <t>opzionale</t>
   </si>
   <si>
-    <t>Stato di nascita</t>
-  </si>
-  <si>
-    <t>Stato di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Provincia di nascita</t>
-  </si>
-  <si>
-    <t>Provincia di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Comune di nascita</t>
-  </si>
-  <si>
-    <t>Comune di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Nazionalità - Descrizione</t>
-  </si>
-  <si>
-    <t>Comprensione</t>
-  </si>
-  <si>
-    <t>tipoImpedimento</t>
-  </si>
-  <si>
-    <t>Stato di residenza</t>
-  </si>
-  <si>
-    <t>Stato di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Provincia di residenza</t>
-  </si>
-  <si>
-    <t>Provincia di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Comune di residenza</t>
-  </si>
-  <si>
-    <t>Comune di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Indirizzo di residenza</t>
-  </si>
-  <si>
-    <t>flag dichiarante</t>
-  </si>
-  <si>
-    <t>flagDichiarante</t>
-  </si>
-  <si>
-    <t>flag comparente</t>
-  </si>
-  <si>
-    <t>flagComparente</t>
-  </si>
-  <si>
-    <t>flag firmatario</t>
-  </si>
-  <si>
-    <t>flagFirmatario</t>
-  </si>
-  <si>
-    <t>Trasmissione residenza estera</t>
-  </si>
-  <si>
-    <t>flagTrasmissioneResidenzaEstera</t>
-  </si>
-  <si>
-    <t>Padre</t>
-  </si>
-  <si>
-    <t>evento.padre</t>
-  </si>
-  <si>
-    <t>Madre biologica</t>
-  </si>
-  <si>
-    <t>evento.madreBiologica</t>
-  </si>
-  <si>
     <t>Padre biologico</t>
   </si>
   <si>
@@ -525,6 +534,15 @@
   </si>
   <si>
     <t>testoLibero</t>
+  </si>
+  <si>
+    <t>Dettagli evento</t>
+  </si>
+  <si>
+    <t>Adozione omogenitoriale</t>
+  </si>
+  <si>
+    <t>flagOmogenitoriale</t>
   </si>
 </sst>
 </file>
@@ -583,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.390625" customWidth="true" bestFit="true"/>
@@ -592,7 +610,7 @@
     <col min="4" max="4" width="24.79296875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="28.44921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="31.45703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2239,7 +2257,7 @@
         <v>27</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>29</v>
@@ -2248,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73">
@@ -2262,7 +2280,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>31</v>
@@ -2271,7 +2289,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74">
@@ -2285,7 +2303,7 @@
         <v>27</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>35</v>
@@ -2294,7 +2312,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75">
@@ -2308,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>37</v>
@@ -2317,7 +2335,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76">
@@ -2331,7 +2349,7 @@
         <v>27</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>39</v>
@@ -2340,7 +2358,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77">
@@ -2354,7 +2372,7 @@
         <v>27</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
@@ -2363,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78">
@@ -2377,7 +2395,7 @@
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>43</v>
@@ -2386,7 +2404,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79">
@@ -2400,7 +2418,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>45</v>
@@ -2409,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80">
@@ -2423,7 +2441,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>47</v>
@@ -2432,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81">
@@ -2446,7 +2464,7 @@
         <v>27</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>49</v>
@@ -2455,7 +2473,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82">
@@ -2469,7 +2487,7 @@
         <v>27</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>51</v>
@@ -2478,7 +2496,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83">
@@ -2492,7 +2510,7 @@
         <v>27</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>53</v>
@@ -2501,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84">
@@ -2515,7 +2533,7 @@
         <v>27</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>55</v>
@@ -2524,7 +2542,7 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85">
@@ -2538,7 +2556,7 @@
         <v>27</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>57</v>
@@ -2547,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86">
@@ -2561,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>59</v>
@@ -2570,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87">
@@ -2584,7 +2602,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>61</v>
@@ -2593,7 +2611,7 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88">
@@ -2607,7 +2625,7 @@
         <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>99</v>
@@ -2616,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89">
@@ -2630,7 +2648,7 @@
         <v>27</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>63</v>
@@ -2639,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90">
@@ -2653,7 +2671,7 @@
         <v>27</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>65</v>
@@ -2662,7 +2680,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91">
@@ -2676,7 +2694,7 @@
         <v>27</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>67</v>
@@ -2685,7 +2703,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92">
@@ -2699,7 +2717,7 @@
         <v>27</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>69</v>
@@ -2708,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93">
@@ -2722,7 +2740,7 @@
         <v>27</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>71</v>
@@ -2731,7 +2749,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94">
@@ -2745,7 +2763,7 @@
         <v>27</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>73</v>
@@ -2754,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
@@ -2768,7 +2786,7 @@
         <v>27</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>75</v>
@@ -2777,7 +2795,7 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96">
@@ -2791,7 +2809,7 @@
         <v>27</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>77</v>
@@ -2800,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97">
@@ -2814,7 +2832,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>108</v>
@@ -2823,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98">
@@ -2837,7 +2855,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>110</v>
@@ -2846,7 +2864,7 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99">
@@ -2860,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>112</v>
@@ -2869,7 +2887,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100">
@@ -2883,7 +2901,7 @@
         <v>27</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>79</v>
@@ -2892,7 +2910,7 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101">
@@ -2906,7 +2924,7 @@
         <v>27</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>81</v>
@@ -2915,7 +2933,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102">
@@ -2929,7 +2947,7 @@
         <v>27</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>83</v>
@@ -2938,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103">
@@ -2952,7 +2970,7 @@
         <v>27</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>85</v>
@@ -2961,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104">
@@ -2975,7 +2993,7 @@
         <v>27</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>114</v>
@@ -2984,12 +3002,12 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>26</v>
@@ -2998,7 +3016,7 @@
         <v>27</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>29</v>
@@ -3012,7 +3030,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>30</v>
@@ -3021,7 +3039,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>31</v>
@@ -3035,7 +3053,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>34</v>
@@ -3044,7 +3062,7 @@
         <v>27</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>35</v>
@@ -3058,7 +3076,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>36</v>
@@ -3067,7 +3085,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>37</v>
@@ -3081,7 +3099,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>38</v>
@@ -3090,7 +3108,7 @@
         <v>27</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>39</v>
@@ -3104,7 +3122,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>40</v>
@@ -3113,7 +3131,7 @@
         <v>27</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>41</v>
@@ -3127,7 +3145,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>42</v>
@@ -3136,7 +3154,7 @@
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>43</v>
@@ -3150,7 +3168,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>91</v>
@@ -3159,7 +3177,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>45</v>
@@ -3173,7 +3191,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>92</v>
@@ -3182,7 +3200,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>47</v>
@@ -3196,7 +3214,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>93</v>
@@ -3205,7 +3223,7 @@
         <v>27</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>49</v>
@@ -3219,7 +3237,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>94</v>
@@ -3228,7 +3246,7 @@
         <v>27</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>51</v>
@@ -3242,7 +3260,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>95</v>
@@ -3251,7 +3269,7 @@
         <v>27</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>53</v>
@@ -3265,7 +3283,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>96</v>
@@ -3274,7 +3292,7 @@
         <v>27</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>55</v>
@@ -3288,7 +3306,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>56</v>
@@ -3297,7 +3315,7 @@
         <v>27</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>57</v>
@@ -3311,7 +3329,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>58</v>
@@ -3320,7 +3338,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>59</v>
@@ -3334,7 +3352,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>97</v>
@@ -3343,7 +3361,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>61</v>
@@ -3357,7 +3375,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>98</v>
@@ -3366,7 +3384,7 @@
         <v>27</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>99</v>
@@ -3380,7 +3398,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>62</v>
@@ -3389,7 +3407,7 @@
         <v>27</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>63</v>
@@ -3403,7 +3421,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>100</v>
@@ -3412,7 +3430,7 @@
         <v>27</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>65</v>
@@ -3426,7 +3444,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>101</v>
@@ -3435,7 +3453,7 @@
         <v>27</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>67</v>
@@ -3449,7 +3467,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>102</v>
@@ -3458,7 +3476,7 @@
         <v>27</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>69</v>
@@ -3472,7 +3490,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>103</v>
@@ -3481,7 +3499,7 @@
         <v>27</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>71</v>
@@ -3495,7 +3513,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>104</v>
@@ -3504,7 +3522,7 @@
         <v>27</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>73</v>
@@ -3518,7 +3536,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>105</v>
@@ -3527,7 +3545,7 @@
         <v>27</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>75</v>
@@ -3541,7 +3559,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>106</v>
@@ -3550,7 +3568,7 @@
         <v>27</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>77</v>
@@ -3564,7 +3582,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>107</v>
@@ -3573,7 +3591,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>108</v>
@@ -3587,7 +3605,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>109</v>
@@ -3596,7 +3614,7 @@
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>110</v>
@@ -3610,7 +3628,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>111</v>
@@ -3619,7 +3637,7 @@
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>112</v>
@@ -3633,7 +3651,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>78</v>
@@ -3642,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>79</v>
@@ -3656,7 +3674,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>80</v>
@@ -3665,7 +3683,7 @@
         <v>27</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>81</v>
@@ -3679,7 +3697,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>82</v>
@@ -3688,7 +3706,7 @@
         <v>27</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>83</v>
@@ -3702,7 +3720,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>84</v>
@@ -3711,7 +3729,7 @@
         <v>27</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>85</v>
@@ -3725,7 +3743,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>113</v>
@@ -3734,7 +3752,7 @@
         <v>27</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>114</v>
@@ -3748,7 +3766,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>26</v>
@@ -3757,7 +3775,7 @@
         <v>27</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>29</v>
@@ -3766,12 +3784,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>30</v>
@@ -3780,7 +3798,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>31</v>
@@ -3789,12 +3807,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>34</v>
@@ -3803,7 +3821,7 @@
         <v>27</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>35</v>
@@ -3812,12 +3830,12 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>36</v>
@@ -3826,7 +3844,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>37</v>
@@ -3835,12 +3853,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>38</v>
@@ -3849,7 +3867,7 @@
         <v>27</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>39</v>
@@ -3858,12 +3876,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>40</v>
@@ -3872,7 +3890,7 @@
         <v>27</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>41</v>
@@ -3881,12 +3899,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>42</v>
@@ -3895,7 +3913,7 @@
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>43</v>
@@ -3904,12 +3922,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>91</v>
@@ -3918,7 +3936,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>45</v>
@@ -3927,12 +3945,12 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>92</v>
@@ -3941,7 +3959,7 @@
         <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>47</v>
@@ -3950,12 +3968,12 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>93</v>
@@ -3964,7 +3982,7 @@
         <v>27</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>49</v>
@@ -3973,12 +3991,12 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>94</v>
@@ -3987,7 +4005,7 @@
         <v>27</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>51</v>
@@ -3996,12 +4014,12 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>95</v>
@@ -4010,7 +4028,7 @@
         <v>27</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>53</v>
@@ -4019,12 +4037,12 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>96</v>
@@ -4033,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>55</v>
@@ -4042,12 +4060,12 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>56</v>
@@ -4056,7 +4074,7 @@
         <v>27</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>57</v>
@@ -4065,12 +4083,12 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>58</v>
@@ -4079,7 +4097,7 @@
         <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>59</v>
@@ -4088,12 +4106,12 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>97</v>
@@ -4102,7 +4120,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>61</v>
@@ -4111,12 +4129,12 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>98</v>
@@ -4125,7 +4143,7 @@
         <v>27</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>99</v>
@@ -4134,12 +4152,12 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>62</v>
@@ -4148,7 +4166,7 @@
         <v>27</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>63</v>
@@ -4157,12 +4175,12 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>100</v>
@@ -4171,7 +4189,7 @@
         <v>27</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>65</v>
@@ -4180,12 +4198,12 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>101</v>
@@ -4194,7 +4212,7 @@
         <v>27</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>67</v>
@@ -4203,12 +4221,12 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>102</v>
@@ -4217,7 +4235,7 @@
         <v>27</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>69</v>
@@ -4226,12 +4244,12 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>103</v>
@@ -4240,7 +4258,7 @@
         <v>27</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>71</v>
@@ -4249,12 +4267,12 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>104</v>
@@ -4263,7 +4281,7 @@
         <v>27</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>73</v>
@@ -4272,12 +4290,12 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>105</v>
@@ -4286,7 +4304,7 @@
         <v>27</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>75</v>
@@ -4295,12 +4313,12 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>106</v>
@@ -4309,7 +4327,7 @@
         <v>27</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>77</v>
@@ -4318,12 +4336,12 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>107</v>
@@ -4332,7 +4350,7 @@
         <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>108</v>
@@ -4341,12 +4359,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>109</v>
@@ -4355,7 +4373,7 @@
         <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>110</v>
@@ -4364,12 +4382,12 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>111</v>
@@ -4378,7 +4396,7 @@
         <v>9</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>112</v>
@@ -4387,12 +4405,12 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>78</v>
@@ -4401,7 +4419,7 @@
         <v>27</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>79</v>
@@ -4410,12 +4428,12 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>80</v>
@@ -4424,7 +4442,7 @@
         <v>27</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>81</v>
@@ -4433,12 +4451,12 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>82</v>
@@ -4447,7 +4465,7 @@
         <v>27</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>83</v>
@@ -4456,12 +4474,12 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>84</v>
@@ -4470,7 +4488,7 @@
         <v>27</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>85</v>
@@ -4479,12 +4497,12 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>113</v>
@@ -4493,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>114</v>
@@ -4502,535 +4520,2076 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>132</v>
+        <v>39</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="F254" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E193" s="2" t="s">
+      <c r="F257" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F193" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G193" s="2" t="s">
+      <c r="C258" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G260" s="2" t="s">
         <v>18</v>
       </c>
     </row>
